--- a/LISTA DE PEÇAS POR MÁQUINA - TRIMMER 1500M2.xlsx
+++ b/LISTA DE PEÇAS POR MÁQUINA - TRIMMER 1500M2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeluzjunior\PycharmProjects\teste_visual\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\pcmauro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB1E9DE-9998-4844-AF95-0AB65A3780A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F08BC9-581E-4D90-8B92-AA48D545520D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="195" yWindow="480" windowWidth="28605" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DADOS" sheetId="2" r:id="rId1"/>
@@ -4861,12 +4861,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5099,19 +5100,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A07255AE-BBDF-48D2-933F-8224645FB75F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B09F593-B1EE-43C0-8142-911C68E497CA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5136,11 +5138,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B09F593-B1EE-43C0-8142-911C68E497CA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A07255AE-BBDF-48D2-933F-8224645FB75F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/LISTA DE PEÇAS POR MÁQUINA - TRIMMER 1500M2.xlsx
+++ b/LISTA DE PEÇAS POR MÁQUINA - TRIMMER 1500M2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\pcmauro\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zeluzjunior\PycharmProjects\teste_visual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F08BC9-581E-4D90-8B92-AA48D545520D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787E4E7F-9BC6-4963-B793-3878A2425401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="195" yWindow="480" windowWidth="28605" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DADOS" sheetId="2" r:id="rId1"/>
@@ -3429,7 +3429,7 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B2" s="5">
         <v>1</v>
@@ -3483,7 +3483,7 @@
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B3" s="5">
         <v>1</v>
@@ -3537,7 +3537,7 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B4" s="5">
         <v>2</v>
@@ -3591,7 +3591,7 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B5" s="5">
         <v>2</v>
@@ -3645,7 +3645,7 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>45</v>
@@ -3699,7 +3699,7 @@
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B7" s="5">
         <v>3</v>
@@ -3753,7 +3753,7 @@
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>45</v>
@@ -3807,7 +3807,7 @@
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>45</v>
@@ -3861,7 +3861,7 @@
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>45</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B11" s="5">
         <v>4</v>
@@ -3969,7 +3969,7 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B12" s="5">
         <v>4</v>
@@ -4023,7 +4023,7 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B13" s="5">
         <v>5</v>
@@ -4077,7 +4077,7 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B14" s="5">
         <v>5</v>
@@ -4131,7 +4131,7 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B15" s="5">
         <v>6</v>
@@ -4185,7 +4185,7 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B16" s="5">
         <v>6</v>
@@ -4239,7 +4239,7 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B17" s="5">
         <v>7</v>
@@ -4293,7 +4293,7 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>45</v>
@@ -4347,7 +4347,7 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B19" s="5">
         <v>8</v>
@@ -4401,7 +4401,7 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B20" s="5">
         <v>9</v>
@@ -4455,7 +4455,7 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B21" s="5">
         <v>9</v>
@@ -4509,7 +4509,7 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B22" s="5">
         <v>10</v>
@@ -4563,7 +4563,7 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B23" s="5">
         <v>11</v>
@@ -4617,7 +4617,7 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B24" s="5">
         <v>11</v>
@@ -4671,7 +4671,7 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B25" s="5">
         <v>12</v>
@@ -4725,7 +4725,7 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>45</v>
@@ -4779,7 +4779,7 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>8195</v>
+        <v>8173</v>
       </c>
       <c r="B27" s="5">
         <v>13</v>
@@ -4833,6 +4833,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
@@ -4861,16 +4862,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010071220A11FEA46C4886D3604CC483AD6B" ma:contentTypeVersion="15" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="bb07fbe832bfbac930195f44faefcab7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2" xmlns:ns3="8de5c96d-c68a-4bc1-8ca7-a6766c74fd4d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="71ce47b93599878504e7d9a94c5299da" ns2:_="" ns3:_="">
     <xsd:import namespace="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2"/>
@@ -5099,7 +5090,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -5108,17 +5099,17 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B09F593-B1EE-43C0-8142-911C68E497CA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8727E901-A346-4E6F-8BBE-9C33480BAED4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5137,10 +5128,20 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A07255AE-BBDF-48D2-933F-8224645FB75F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B09F593-B1EE-43C0-8142-911C68E497CA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="6dbcbc56-3d12-411a-a735-f36ec8e8bfd2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>